--- a/results.xlsx
+++ b/results.xlsx
@@ -1,22 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\NetworkValuationML\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F94006B8-C9DF-440C-A117-4E6A1B0AD897}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{988189A1-D820-4B6A-A0B9-1BACD280F842}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{B1C19E24-EBF5-44D1-92BE-26D6EBACA9C1}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" firstSheet="1" activeTab="1" xr2:uid="{B1C19E24-EBF5-44D1-92BE-26D6EBACA9C1}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="6" r:id="rId1"/>
     <sheet name="plot_haircut" sheetId="5" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -407,91 +408,91 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="29"/>
                 <c:pt idx="0">
-                  <c:v>3.3097133040428099E-2</c:v>
+                  <c:v>3.3751554787158897E-2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>3.34039106965065E-2</c:v>
+                  <c:v>3.3286988735198898E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3.6625843495130497E-2</c:v>
+                  <c:v>3.39981764554977E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3.7351232022047001E-2</c:v>
+                  <c:v>3.6743033677339498E-2</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>3.55173237621784E-2</c:v>
+                  <c:v>3.84357534348964E-2</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>4.2434971779584801E-2</c:v>
+                  <c:v>3.8134638220071702E-2</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>4.2206224054098102E-2</c:v>
+                  <c:v>4.0744956582784597E-2</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>4.5808106660842798E-2</c:v>
+                  <c:v>4.3086457997560501E-2</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>4.8407293856143903E-2</c:v>
+                  <c:v>4.59185391664505E-2</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>5.1805626600980703E-2</c:v>
+                  <c:v>4.8882380127906799E-2</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>5.4882191121578203E-2</c:v>
+                  <c:v>5.0366409122943802E-2</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>5.5902875959873199E-2</c:v>
+                  <c:v>5.6311883032321902E-2</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>5.9801079332828501E-2</c:v>
+                  <c:v>6.0192506760358797E-2</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>5.8628033846616703E-2</c:v>
+                  <c:v>6.7653633654117501E-2</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>6.5848812460899298E-2</c:v>
+                  <c:v>7.8118994832038796E-2</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>7.6677277684211703E-2</c:v>
+                  <c:v>8.4123998880386297E-2</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>8.17932039499282E-2</c:v>
+                  <c:v>9.0567603707313496E-2</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>8.9623406529426505E-2</c:v>
+                  <c:v>9.1945864260196603E-2</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>8.9054353535175296E-2</c:v>
+                  <c:v>9.7464814782142598E-2</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>9.7915522754192297E-2</c:v>
+                  <c:v>0.104607567191123</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.101141847670078</c:v>
+                  <c:v>0.106722012162208</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.106459125876426</c:v>
+                  <c:v>0.112384460866451</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.113283716142177</c:v>
+                  <c:v>0.117901608347892</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.111504673957824</c:v>
+                  <c:v>0.12214259803295099</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.11835602670907901</c:v>
+                  <c:v>0.12701520323753299</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.12065558135509399</c:v>
+                  <c:v>0.12770959734916601</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.12165930122137</c:v>
+                  <c:v>0.12409780174493699</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.111503697931766</c:v>
+                  <c:v>0.113070309162139</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>7.4504397809505393E-2</c:v>
+                  <c:v>7.0693328976631095E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -644,91 +645,91 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="29"/>
                 <c:pt idx="0">
-                  <c:v>3.8046400994062403E-2</c:v>
+                  <c:v>3.5656787455081898E-2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>3.6460347473621299E-2</c:v>
+                  <c:v>3.8199134171009001E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3.9260558784007998E-2</c:v>
+                  <c:v>3.7197634577751097E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3.98269668221473E-2</c:v>
+                  <c:v>3.81886325776577E-2</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>4.1383035480976098E-2</c:v>
+                  <c:v>4.3317735195159898E-2</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>4.5963644981384201E-2</c:v>
+                  <c:v>4.5128595083951902E-2</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>4.8852600157260798E-2</c:v>
+                  <c:v>4.7143045812845202E-2</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>5.1663864403962999E-2</c:v>
+                  <c:v>4.7910138964653001E-2</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>5.2419353276491103E-2</c:v>
+                  <c:v>5.15178963541984E-2</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>5.9359502047300297E-2</c:v>
+                  <c:v>5.60634210705757E-2</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>5.8799069374799701E-2</c:v>
+                  <c:v>5.6190323084592798E-2</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>6.3893094658851596E-2</c:v>
+                  <c:v>6.3178442418575204E-2</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>6.8753980100154793E-2</c:v>
+                  <c:v>6.6661335527896798E-2</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>7.0506140589713995E-2</c:v>
+                  <c:v>7.0105440914630807E-2</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>7.4017629027366597E-2</c:v>
+                  <c:v>7.5779266655445099E-2</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>8.1552281975746099E-2</c:v>
+                  <c:v>7.8612394630908897E-2</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>8.6063131690025302E-2</c:v>
+                  <c:v>8.2558639347553198E-2</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>9.1308340430259705E-2</c:v>
+                  <c:v>8.7971575558185494E-2</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>9.5183745026588398E-2</c:v>
+                  <c:v>9.4709157943725503E-2</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>9.9942266941070501E-2</c:v>
+                  <c:v>9.9128834903240204E-2</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.100645676255226</c:v>
+                  <c:v>0.10222329199314099</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.10307927429676</c:v>
+                  <c:v>0.103443525731563</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.108763262629508</c:v>
+                  <c:v>0.10684435069561</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.109025754034519</c:v>
+                  <c:v>0.10960235446691501</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.113086029887199</c:v>
+                  <c:v>0.10987424850463801</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.10916151851415599</c:v>
+                  <c:v>0.109856463968753</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.10881374776363301</c:v>
+                  <c:v>0.107993103563785</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>9.8520576953887898E-2</c:v>
+                  <c:v>0.100706323981285</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>7.3779247701168005E-2</c:v>
+                  <c:v>7.2700567543506595E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5354,10 +5355,10 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>3.3097133040428099E-2</v>
+        <v>3.3751554787158897E-2</v>
       </c>
       <c r="C2">
-        <v>3.8046400994062403E-2</v>
+        <v>3.5656787455081898E-2</v>
       </c>
       <c r="D2">
         <v>3.3954970538616097E-2</v>
@@ -5395,10 +5396,10 @@
         <v>4.2099999999999999E-2</v>
       </c>
       <c r="B3">
-        <v>3.34039106965065E-2</v>
+        <v>3.3286988735198898E-2</v>
       </c>
       <c r="C3">
-        <v>3.6460347473621299E-2</v>
+        <v>3.8199134171009001E-2</v>
       </c>
       <c r="D3">
         <v>3.6325372755527399E-2</v>
@@ -5436,10 +5437,10 @@
         <v>8.4199999999999997E-2</v>
       </c>
       <c r="B4">
-        <v>3.6625843495130497E-2</v>
+        <v>3.39981764554977E-2</v>
       </c>
       <c r="C4">
-        <v>3.9260558784007998E-2</v>
+        <v>3.7197634577751097E-2</v>
       </c>
       <c r="D4">
         <v>3.8168109953403397E-2</v>
@@ -5477,10 +5478,10 @@
         <v>0.1263</v>
       </c>
       <c r="B5">
-        <v>3.7351232022047001E-2</v>
+        <v>3.6743033677339498E-2</v>
       </c>
       <c r="C5">
-        <v>3.98269668221473E-2</v>
+        <v>3.81886325776577E-2</v>
       </c>
       <c r="D5">
         <v>4.0801830589771201E-2</v>
@@ -5518,10 +5519,10 @@
         <v>0.16839999999999999</v>
       </c>
       <c r="B6">
-        <v>3.55173237621784E-2</v>
+        <v>3.84357534348964E-2</v>
       </c>
       <c r="C6">
-        <v>4.1383035480976098E-2</v>
+        <v>4.3317735195159898E-2</v>
       </c>
       <c r="D6">
         <v>4.1854366660118103E-2</v>
@@ -5559,10 +5560,10 @@
         <v>0.21049999999999999</v>
       </c>
       <c r="B7">
-        <v>4.2434971779584801E-2</v>
+        <v>3.8134638220071702E-2</v>
       </c>
       <c r="C7">
-        <v>4.5963644981384201E-2</v>
+        <v>4.5128595083951902E-2</v>
       </c>
       <c r="D7">
         <v>4.5388750731945003E-2</v>
@@ -5600,10 +5601,10 @@
         <v>0.25259999999999999</v>
       </c>
       <c r="B8">
-        <v>4.2206224054098102E-2</v>
+        <v>4.0744956582784597E-2</v>
       </c>
       <c r="C8">
-        <v>4.8852600157260798E-2</v>
+        <v>4.7143045812845202E-2</v>
       </c>
       <c r="D8">
         <v>4.7419462352991097E-2</v>
@@ -5641,10 +5642,10 @@
         <v>0.29470000000000002</v>
       </c>
       <c r="B9">
-        <v>4.5808106660842798E-2</v>
+        <v>4.3086457997560501E-2</v>
       </c>
       <c r="C9">
-        <v>5.1663864403962999E-2</v>
+        <v>4.7910138964653001E-2</v>
       </c>
       <c r="D9">
         <v>4.9400888383388498E-2</v>
@@ -5682,10 +5683,10 @@
         <v>0.33679999999999999</v>
       </c>
       <c r="B10">
-        <v>4.8407293856143903E-2</v>
+        <v>4.59185391664505E-2</v>
       </c>
       <c r="C10">
-        <v>5.2419353276491103E-2</v>
+        <v>5.15178963541984E-2</v>
       </c>
       <c r="D10">
         <v>5.3792905062437002E-2</v>
@@ -5723,10 +5724,10 @@
         <v>0.37890000000000001</v>
       </c>
       <c r="B11">
-        <v>5.1805626600980703E-2</v>
+        <v>4.8882380127906799E-2</v>
       </c>
       <c r="C11">
-        <v>5.9359502047300297E-2</v>
+        <v>5.60634210705757E-2</v>
       </c>
       <c r="D11">
         <v>5.5877733975648797E-2</v>
@@ -5764,10 +5765,10 @@
         <v>0.42109999999999997</v>
       </c>
       <c r="B12">
-        <v>5.4882191121578203E-2</v>
+        <v>5.0366409122943802E-2</v>
       </c>
       <c r="C12">
-        <v>5.8799069374799701E-2</v>
+        <v>5.6190323084592798E-2</v>
       </c>
       <c r="D12">
         <v>6.0807157307863201E-2</v>
@@ -5805,10 +5806,10 @@
         <v>0.4632</v>
       </c>
       <c r="B13">
-        <v>5.5902875959873199E-2</v>
+        <v>5.6311883032321902E-2</v>
       </c>
       <c r="C13">
-        <v>6.3893094658851596E-2</v>
+        <v>6.3178442418575204E-2</v>
       </c>
       <c r="D13">
         <v>6.3395813107490498E-2</v>
@@ -5846,10 +5847,10 @@
         <v>0.50529999999999997</v>
       </c>
       <c r="B14">
-        <v>5.9801079332828501E-2</v>
+        <v>6.0192506760358797E-2</v>
       </c>
       <c r="C14">
-        <v>6.8753980100154793E-2</v>
+        <v>6.6661335527896798E-2</v>
       </c>
       <c r="D14">
         <v>6.6846929490566198E-2</v>
@@ -5887,10 +5888,10 @@
         <v>0.5474</v>
       </c>
       <c r="B15">
-        <v>5.8628033846616703E-2</v>
+        <v>6.7653633654117501E-2</v>
       </c>
       <c r="C15">
-        <v>7.0506140589713995E-2</v>
+        <v>7.0105440914630807E-2</v>
       </c>
       <c r="D15">
         <v>7.1113951504230499E-2</v>
@@ -5928,10 +5929,10 @@
         <v>0.58950000000000002</v>
       </c>
       <c r="B16">
-        <v>6.5848812460899298E-2</v>
+        <v>7.8118994832038796E-2</v>
       </c>
       <c r="C16">
-        <v>7.4017629027366597E-2</v>
+        <v>7.5779266655445099E-2</v>
       </c>
       <c r="D16">
         <v>7.7016249299049294E-2</v>
@@ -5969,10 +5970,10 @@
         <v>0.63160000000000005</v>
       </c>
       <c r="B17">
-        <v>7.6677277684211703E-2</v>
+        <v>8.4123998880386297E-2</v>
       </c>
       <c r="C17">
-        <v>8.1552281975746099E-2</v>
+        <v>7.8612394630908897E-2</v>
       </c>
       <c r="D17">
         <v>8.0131880939006805E-2</v>
@@ -6010,10 +6011,10 @@
         <v>0.67369999999999997</v>
       </c>
       <c r="B18">
-        <v>8.17932039499282E-2</v>
+        <v>9.0567603707313496E-2</v>
       </c>
       <c r="C18">
-        <v>8.6063131690025302E-2</v>
+        <v>8.2558639347553198E-2</v>
       </c>
       <c r="D18">
         <v>8.5982836782932198E-2</v>
@@ -6051,10 +6052,10 @@
         <v>0.71579999999999999</v>
       </c>
       <c r="B19">
-        <v>8.9623406529426505E-2</v>
+        <v>9.1945864260196603E-2</v>
       </c>
       <c r="C19">
-        <v>9.1308340430259705E-2</v>
+        <v>8.7971575558185494E-2</v>
       </c>
       <c r="D19">
         <v>8.9532613754272405E-2</v>
@@ -6092,10 +6093,10 @@
         <v>0.75790000000000002</v>
       </c>
       <c r="B20">
-        <v>8.9054353535175296E-2</v>
+        <v>9.7464814782142598E-2</v>
       </c>
       <c r="C20">
-        <v>9.5183745026588398E-2</v>
+        <v>9.4709157943725503E-2</v>
       </c>
       <c r="D20">
         <v>9.5837689936161E-2</v>
@@ -6133,10 +6134,10 @@
         <v>0.8</v>
       </c>
       <c r="B21">
-        <v>9.7915522754192297E-2</v>
+        <v>0.104607567191123</v>
       </c>
       <c r="C21">
-        <v>9.9942266941070501E-2</v>
+        <v>9.9128834903240204E-2</v>
       </c>
       <c r="D21">
         <v>9.6241071820259094E-2</v>
@@ -6174,10 +6175,10 @@
         <v>0.82220000000000004</v>
       </c>
       <c r="B22">
-        <v>0.101141847670078</v>
+        <v>0.106722012162208</v>
       </c>
       <c r="C22">
-        <v>0.100645676255226</v>
+        <v>0.10222329199314099</v>
       </c>
       <c r="D22">
         <v>9.9360011518001501E-2</v>
@@ -6215,10 +6216,10 @@
         <v>0.84440000000000004</v>
       </c>
       <c r="B23">
-        <v>0.106459125876426</v>
+        <v>0.112384460866451</v>
       </c>
       <c r="C23">
-        <v>0.10307927429676</v>
+        <v>0.103443525731563</v>
       </c>
       <c r="D23">
         <v>0.10202948749065301</v>
@@ -6256,10 +6257,10 @@
         <v>0.86670000000000003</v>
       </c>
       <c r="B24">
-        <v>0.113283716142177</v>
+        <v>0.117901608347892</v>
       </c>
       <c r="C24">
-        <v>0.108763262629508</v>
+        <v>0.10684435069561</v>
       </c>
       <c r="D24">
         <v>0.10334938764572101</v>
@@ -6297,10 +6298,10 @@
         <v>0.88890000000000002</v>
       </c>
       <c r="B25">
-        <v>0.111504673957824</v>
+        <v>0.12214259803295099</v>
       </c>
       <c r="C25">
-        <v>0.109025754034519</v>
+        <v>0.10960235446691501</v>
       </c>
       <c r="D25">
         <v>0.10504722595214799</v>
@@ -6338,10 +6339,10 @@
         <v>0.91110000000000002</v>
       </c>
       <c r="B26">
-        <v>0.11835602670907901</v>
+        <v>0.12701520323753299</v>
       </c>
       <c r="C26">
-        <v>0.113086029887199</v>
+        <v>0.10987424850463801</v>
       </c>
       <c r="D26">
         <v>0.105311550199985</v>
@@ -6379,10 +6380,10 @@
         <v>0.93330000000000002</v>
       </c>
       <c r="B27">
-        <v>0.12065558135509399</v>
+        <v>0.12770959734916601</v>
       </c>
       <c r="C27">
-        <v>0.10916151851415599</v>
+        <v>0.109856463968753</v>
       </c>
       <c r="D27">
         <v>0.109254218637943</v>
@@ -6420,10 +6421,10 @@
         <v>0.9556</v>
       </c>
       <c r="B28">
-        <v>0.12165930122137</v>
+        <v>0.12409780174493699</v>
       </c>
       <c r="C28">
-        <v>0.10881374776363301</v>
+        <v>0.107993103563785</v>
       </c>
       <c r="D28">
         <v>0.10703605413436799</v>
@@ -6461,10 +6462,10 @@
         <v>0.9778</v>
       </c>
       <c r="B29">
-        <v>0.111503697931766</v>
+        <v>0.113070309162139</v>
       </c>
       <c r="C29">
-        <v>9.8520576953887898E-2</v>
+        <v>0.100706323981285</v>
       </c>
       <c r="D29">
         <v>0.100036241114139</v>
@@ -6502,10 +6503,10 @@
         <v>1</v>
       </c>
       <c r="B30">
-        <v>7.4504397809505393E-2</v>
+        <v>7.0693328976631095E-2</v>
       </c>
       <c r="C30">
-        <v>7.3779247701168005E-2</v>
+        <v>7.2700567543506595E-2</v>
       </c>
       <c r="D30">
         <v>7.1105502545833504E-2</v>
